--- a/Output-Excel/BM_26-27_1328.xlsx
+++ b/Output-Excel/BM_26-27_1328.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5100002309</t>
+          <t>PO-5100002309</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,11 @@
           <t>Vendor Code</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -632,7 +636,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>500356389</t>
+          <t>S00356389</t>
         </is>
       </c>
     </row>
@@ -766,7 +770,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>405x255mm-1.2714 Db6-72284000 BHN 397</t>
+          <t>405x255mm 1.2714 Db6-72284000 BHN 397</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -790,7 +794,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>405x255mm-1.2714 Db6-72284000 BHN 396</t>
+          <t>405x255mm 1.2714 Db6-72284000 BHN 396</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -814,7 +818,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>405x255mm-1.2714 Db6-72284000 BHN 392</t>
+          <t>405x255mm 1.2714 Db6-72284000 BHN 392</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -838,11 +842,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>405x255mm-1.2714 Db6-72284000 BHN 382</t>
+          <t>405x255mm 1.2714 Db6-72284000 BHN 382</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>158.4</v>
+        <v>156.4</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>210</v>
@@ -853,7 +857,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>33264</v>
+        <v>32844</v>
       </c>
     </row>
     <row r="8">
@@ -862,7 +866,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>405x255mm-1.2714 Db6-72284000 BHN 383</t>
+          <t>405x255mm 1.2714 Db6-72284000 BHN 383</t>
         </is>
       </c>
       <c r="C8" t="n">

--- a/Output-Excel/BM_26-27_1328.xlsx
+++ b/Output-Excel/BM_26-27_1328.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PO-5100002309</t>
+          <t>5100002309</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>27AAACM0618A1ZZ</t>
+          <t>27AABCK0618A1Z7</t>
         </is>
       </c>
     </row>
@@ -550,11 +550,7 @@
           <t>Vendor Code</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -636,7 +632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>S00356389</t>
+          <t>50035689</t>
         </is>
       </c>
     </row>
@@ -659,7 +655,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -846,7 +842,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>156.4</v>
+        <v>158.4</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>210</v>
@@ -857,7 +853,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>32844</v>
+        <v>33264</v>
       </c>
     </row>
     <row r="8">

--- a/Output-Excel/BM_26-27_1328.xlsx
+++ b/Output-Excel/BM_26-27_1328.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Line Items" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Status Check" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SAP Check" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +31,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -46,12 +50,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE0A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00145A32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F1D1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F6000"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,14 +86,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,11 +468,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,6 +487,11 @@
           <t>Value</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,191 +504,420 @@
           <t>5000356389.pdf</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>BHARAT METALS 26-27</t>
-        </is>
-      </c>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BHARAT METALS 26-27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>BM/26-27/1328</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Invoice Date</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>PO Number</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>5100002309</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Vendor GSTIN</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>27AABCK0618A1Z7</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSN / SAC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>72284000</t>
-        </is>
-      </c>
+          <t>All POs</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Vendor Code</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Multi-PO Red Flag</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
+          <t>Red Flag Reason</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>184020</v>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PO Date</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CGST</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>16561.8</v>
+          <t>Vendor GSTIN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27AAECK0618A1ZZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SGST</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>16561.8</v>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Vendor Code</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IGST</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Total Tax</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>33123.6</v>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Plant Source</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Invoice Total</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>217144</v>
+          <t>HSN / SAC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>72284000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>GRN / Inward Number</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>50035689</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Handwritten References</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21-8-26</t>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>184020</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VISION</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>16561.8</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>16561.8</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Tax</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>33123.6</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Invoice Total</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>217144</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GST % (total)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>GST % (each half)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GST Type</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CGST_SGST</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>GST Tax Code</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tax Code Description</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PO/GR Tax Code (SAP)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tax Code Match</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>GRN Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>5003563892</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GRN Date</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>GRN Value (SAP)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Handwritten Refs</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>AI Confidence %</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B35" s="4" t="n">
         <v>90</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -669,46 +931,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Sl.No</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Item / Description</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Sl</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>UoM</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>HSN/SAC</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>PO Item</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -724,40 +1016,66 @@
       <c r="C2" t="n">
         <v>45.4</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>210</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>9534</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>405x305mm 1.2714 db6 72284000 BHN 393</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" t="n">
         <v>83</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>210</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" t="n">
         <v>17430</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -766,46 +1084,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>405x255mm 1.2714 Db6-72284000 BHN 397</t>
+          <t>405x255mm-1.2714 Db6-72284000 BHN 397</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>113.8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>210</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>23898</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>405x255mm 1.2714 Db6-72284000 BHN 396</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>405x255mm-1.2714 Db6-72284000 BHN 396</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>123</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>210</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" t="n">
         <v>25830</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -814,46 +1158,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>405x255mm 1.2714 Db6-72284000 BHN 392</t>
+          <t>405x255mm-1.2714 Db6-72284000 BHN 392</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>127.6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>210</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>26796</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>405x255mm 1.2714 Db6-72284000 BHN 382</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>405x255mm-1.2714 Db6-72284000 BHN 382</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>158.4</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>210</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" t="n">
         <v>33264</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -862,46 +1232,72 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>405x255mm 1.2714 Db6-72284000 BHN 383</t>
+          <t>405x255mm-1.2714 Db6-72284000 BHN 383</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>169.8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>210</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>35658</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>142mm 1.2714 DBG 72284000 BHN 381</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>210</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" t="n">
         <v>3360</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -916,40 +1312,66 @@
       <c r="C10" t="n">
         <v>3.4</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>210</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>714</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>505x310mm 1.2714 Db6 72284000 BHN 405</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" t="n">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>210</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" t="n">
         <v>7140</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -964,16 +1386,145 @@
       <c r="C12" t="n">
         <v>3.2</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>255</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>72284000</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>816</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>VISION</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Vendor code missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Plant missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GST tax code missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DOUBT</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SAP not checked — status cannot be confirmed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAP disabled — no cross-check done</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No input tax code in GST master for 9.0%+9.0% (total 18.0%) CGST_SGST</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Output-Excel/BM_26-27_1328.xlsx
+++ b/Output-Excel/BM_26-27_1328.xlsx
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0A3"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -94,13 +99,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -514,7 +520,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -593,7 +599,11 @@
           <t>All POs</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5100002309</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -619,13 +629,21 @@
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>PO Date</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>18.08.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>SAP_EKKO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -645,22 +663,38 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Vendor Code</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>500023</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>SAP_EKKO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>SAP_MSEG</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -668,7 +702,11 @@
           <t>Plant Source</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>SAP_MSEG</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -689,19 +727,19 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>VISION</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>SAP_EKKO</t>
         </is>
       </c>
     </row>
@@ -792,15 +830,19 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>GST % (total)</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -827,13 +869,21 @@
       <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>GST Tax Code</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>GST_MASTER</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -841,17 +891,29 @@
           <t>Tax Code Description</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Input CGST+SGST @ 9%+9%</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>PO/GR Tax Code (SAP)</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>SAP_EKPO</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -859,6 +921,11 @@
           <t>Tax Code Match</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -879,22 +946,36 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>GRN Date</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>22.08.2026</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>SAP_MSEG</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>GRN Value (SAP)</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="inlineStr"/>
+      <c r="B33" s="5" t="n">
+        <v>184020</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>SAP_MSEG</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -948,57 +1029,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Sl</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>HSN/SAC</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>PO Item</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1034,7 +1115,11 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1071,7 +1156,11 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1108,7 +1197,11 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1145,7 +1238,11 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1182,7 +1279,11 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1219,7 +1320,11 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1256,7 +1361,11 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1293,7 +1402,11 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1330,7 +1443,11 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1367,7 +1484,11 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1404,7 +1525,11 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>VISION</t>
@@ -1422,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1430,12 +1555,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Message</t>
         </is>
@@ -1444,48 +1569,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Vendor code missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Plant missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>GST tax code missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>DOUBT</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SAP not checked — status cannot be confirmed</t>
+          <t>All fields filled and matched with SAP — ready for MIRO</t>
         </is>
       </c>
     </row>
@@ -1500,14 +1589,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1516,14 +1605,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAP disabled — no cross-check done</t>
+          <t>GRN 5003563892 NOT found in MSEG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>No input tax code in GST master for 9.0%+9.0% (total 18.0%) CGST_SGST</t>
+          <t>grn_date ← SAP_MSEG: 22.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>plant_code ← SAP_MSEG: 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>vendor_code ← SAP_EKKO: 500023</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>po_date ← SAP_EKKO: 18.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sap_tax_code ← SAP_EKPO: I3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GST 9.0%+9.0% (total 18.0%) CGST_SGST → tax code I3 (Input CGST+SGST @ 9%+9%)</t>
         </is>
       </c>
     </row>

--- a/Output-Excel/BM_26-27_1328.xlsx
+++ b/Output-Excel/BM_26-27_1328.xlsx
@@ -929,19 +929,19 @@
       <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>GRN Number</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>5003563892</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>VISION</t>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>5000356389</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>SAP_MSEG</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1605,47 +1605,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GRN 5003563892 NOT found in MSEG</t>
+          <t>GRN 5003563892 (read from stamp) NOT found in MSEG — looking it up by invoice no / PO / line items</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>grn_date ← SAP_MSEG: 22.08.2026</t>
+          <t>GRN 5003563892 (stamp) → 5000356389 taken from SAP (invoice BM/26-27/1328 / PO 5100002309)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>plant_code ← SAP_MSEG: 2002</t>
+          <t>grn_date ← SAP_MSEG: 22.08.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vendor_code ← SAP_EKKO: 500023</t>
+          <t>plant_code ← SAP_MSEG: 2002</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>po_date ← SAP_EKKO: 18.08.2026</t>
+          <t>vendor_code ← SAP_EKKO: 500023</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sap_tax_code ← SAP_EKPO: I3</t>
+          <t>po_date ← SAP_EKKO: 18.08.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>sap_tax_code ← SAP_EKPO: I3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>GST 9.0%+9.0% (total 18.0%) CGST_SGST → tax code I3 (Input CGST+SGST @ 9%+9%)</t>
         </is>

--- a/Output-Excel/BM_26-27_1328.xlsx
+++ b/Output-Excel/BM_26-27_1328.xlsx
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -50,7 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFE0A3"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,6 +75,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="007F6000"/>
       </patternFill>
     </fill>
@@ -91,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -106,7 +111,8 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,7 +526,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>MATCHED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -609,7 +615,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Multi-PO Red Flag</t>
+          <t>Multiple POs in SAP (Manual)</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -929,19 +935,19 @@
       <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>GRN Number</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>5000356389</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>SAP_MSEG</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>VISION</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1573,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>All fields filled and matched with SAP — ready for MIRO</t>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Line '405x255mm-1.2714 Db6-72284000 BHN 3' qty 158.4 / amount 33,264.00 not found in SAP GR (GRN 5000356389)</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1602,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1605,49 +1611,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GRN 5003563892 (read from stamp) NOT found in MSEG — looking it up by invoice no / PO / line items</t>
+          <t>grn_date ← SAP_MSEG: 22.08.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRN 5003563892 (stamp) → 5000356389 taken from SAP (invoice BM/26-27/1328 / PO 5100002309)</t>
+          <t>plant_code ← SAP_MSEG: 2002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>grn_date ← SAP_MSEG: 22.08.2026</t>
+          <t>vendor_code ← SAP_EKKO: 500023</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>plant_code ← SAP_MSEG: 2002</t>
+          <t>po_date ← SAP_EKKO: 18.08.2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vendor_code ← SAP_EKKO: 500023</t>
+          <t>sap_tax_code ← SAP_EKPO: I3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>po_date ← SAP_EKKO: 18.08.2026</t>
+          <t>1 SAP GR rows are not matched to any invoice line (e.g. DIN 1.2714 - 370 X 250 X 175 qty 156.4)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sap_tax_code ← SAP_EKPO: I3</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>MISMATCH Line '405x255mm-1.2714 Db6-72284000 BHN 3' qty 158.4 / amount 33,264.00 not found in SAP GR (GRN 5000356389)</t>
         </is>
       </c>
     </row>
